--- a/modified_amino_acids_library.xlsx
+++ b/modified_amino_acids_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielgarzonotero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06849F69-A1B9-8244-B5B8-A332D9D14325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EA19AF8-F66C-7746-A470-1C80F0EF71F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="110">
+  <futureMetadata name="XLRICHVALUE" count="105">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -779,43 +779,8 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="105"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="106"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="107"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="108"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="109"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="110">
+  <valueMetadata count="105">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1130,28 +1095,13 @@
     </bk>
     <bk>
       <rc t="1" v="104"/>
-    </bk>
-    <bk>
-      <rc t="1" v="105"/>
-    </bk>
-    <bk>
-      <rc t="1" v="106"/>
-    </bk>
-    <bk>
-      <rc t="1" v="107"/>
-    </bk>
-    <bk>
-      <rc t="1" v="108"/>
-    </bk>
-    <bk>
-      <rc t="1" v="109"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="410">
   <si>
     <t>#</t>
   </si>
@@ -1822,9 +1772,6 @@
     <t>ND</t>
   </si>
   <si>
-    <t>Just for first position</t>
-  </si>
-  <si>
     <t>D-Allyl-Glycine</t>
   </si>
   <si>
@@ -1898,7 +1845,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H]([C@H](C)(CC))C(=O)O(CCOCCOCC(=O)O)</t>
+      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
     </r>
   </si>
   <si>
@@ -1918,7 +1865,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H]([C@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
+      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
     </r>
   </si>
   <si>
@@ -1938,7 +1885,40 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H]([C@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
+      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC=1NC=NC1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
     </r>
   </si>
   <si>
@@ -1953,12 +1933,2657 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC=1NC=NC1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCCCN)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCN)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccccc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccccc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1c[nH]c2ccccc12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1c[nH]c2ccccc12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCSC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCSC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CCC[C@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CCC[C@@H]1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C(=O)C[C@H](N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C(=O)C[C@@H](N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C(C)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCC(=O)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc(O)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc(O)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCC(=O)O)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C(CO))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(CO))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@H](C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CS(CNC(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CS(CNC(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc(OC)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc(OC)cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1c(C)cc(O)cc(C)1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1c(C)cc(O)cc(C)1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](C(C1=CC2=CC=CC=C2C=C1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(C1=CC2=CC=CC=C2C=C1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=O)CCCC[C@@H]1[C@@H]2NC(=O)N[C@@H]2CS1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)CCCCCNC(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=O)C1=CC=C(C(=O)C2=CC=CC=C2)C=C1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=O)C1C=CC(C(=O)C2=CC=CC=C2)=CC=1)[C@H](CCCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C([N]=[N+]=[N-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCNC(=N)N([N+](=O)[O-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCN(C(=O)C))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1CCC[C@@H]1C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCCCNC(=N)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCCCNC(=N)N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CCNC(N)=N)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CCC(C)1N=N1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C(=S)N(C1=CC=C(C2=C1C(=O)OC23C4=C(C=C(C=C4)O)OC5=C3C=CC(=C5)O)))CCCCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC1C=CC(C(=O)O)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C(=O)O)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H](CC1C=CC(C)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC=C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](C(C1C=CC=CC=1)(C1C=CC=CC=1))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC=C(C)C=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C2C=CC=CC=2)=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H](CC1C=CC(C(C)(C)(C))=CC=1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>Exception</t>
+  </si>
+  <si>
+    <t>D-Propargylglycine</t>
+  </si>
+  <si>
+    <t>{pra}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H]([C@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
+      <t>[C@@H](CC#C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
     </r>
   </si>
   <si>
@@ -1978,8 +4603,130 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
-    </r>
+      <t>[C@H](CC#C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>[NH2]</t>
+  </si>
+  <si>
+    <t>71-00-1</t>
+  </si>
+  <si>
+    <t>351-50-8</t>
+  </si>
+  <si>
+    <t>74-79-3</t>
+  </si>
+  <si>
+    <t>157-06-2</t>
+  </si>
+  <si>
+    <t>56-87-1</t>
+  </si>
+  <si>
+    <t>923-27-3</t>
+  </si>
+  <si>
+    <t>73-32-5</t>
+  </si>
+  <si>
+    <t>319-78-8</t>
+  </si>
+  <si>
+    <t>63-91-2</t>
+  </si>
+  <si>
+    <t>673-06-3</t>
+  </si>
+  <si>
+    <t>61-90-5</t>
+  </si>
+  <si>
+    <t>328-38-1</t>
+  </si>
+  <si>
+    <t>54-12-6</t>
+  </si>
+  <si>
+    <t>153-94-6</t>
+  </si>
+  <si>
+    <t>56-41-7</t>
+  </si>
+  <si>
+    <t>338-69-2</t>
+  </si>
+  <si>
+    <t>63-68-3</t>
+  </si>
+  <si>
+    <t>348-67-4</t>
+  </si>
+  <si>
+    <t>147-85-3</t>
+  </si>
+  <si>
+    <t>344-25-2</t>
+  </si>
+  <si>
+    <t>52-90-4</t>
+  </si>
+  <si>
+    <t>921-01-7</t>
+  </si>
+  <si>
+    <t>70-47-3</t>
+  </si>
+  <si>
+    <t>2058-58-4</t>
+  </si>
+  <si>
+    <t>72-18-4</t>
+  </si>
+  <si>
+    <t>640-68-6</t>
+  </si>
+  <si>
+    <t>56-40-6</t>
+  </si>
+  <si>
+    <t>56-45-1</t>
+  </si>
+  <si>
+    <t>312-84-5</t>
+  </si>
+  <si>
+    <t>26700-71-0</t>
+  </si>
+  <si>
+    <t>5959-95-5</t>
+  </si>
+  <si>
+    <t>60-18-4</t>
+  </si>
+  <si>
+    <t>556-02-5</t>
+  </si>
+  <si>
+    <t>56-84-8</t>
+  </si>
+  <si>
+    <t>1783-96-6</t>
+  </si>
+  <si>
+    <t>56-86-0</t>
+  </si>
+  <si>
+    <t>6893-26-1</t>
   </si>
   <si>
     <r>
@@ -1993,13 +4740,306 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>80-68-2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <t>672-15-1</t>
+  </si>
+  <si>
+    <t>6027-21-0</t>
+  </si>
+  <si>
+    <t>3913-67-5</t>
+  </si>
+  <si>
+    <t>600-21-5</t>
+  </si>
+  <si>
+    <t>19647-70-2</t>
+  </si>
+  <si>
+    <t>168300-88-7</t>
+  </si>
+  <si>
+    <t>6230-11-1</t>
+  </si>
+  <si>
+    <t>201335-88-8</t>
+  </si>
+  <si>
+    <t>206060-54-0</t>
+  </si>
+  <si>
+    <t>136771-16-9</t>
+  </si>
+  <si>
+    <t>2812-28-4</t>
+  </si>
+  <si>
+    <t>2812-27-3</t>
+  </si>
+  <si>
+    <t>56-12-2</t>
+  </si>
+  <si>
+    <t>144-98-9</t>
+  </si>
+  <si>
+    <t>24830-94-2</t>
+  </si>
+  <si>
+    <t>76985-09-6</t>
+  </si>
+  <si>
+    <t>58438-03-2</t>
+  </si>
+  <si>
+    <t>741281-41-4</t>
+  </si>
+  <si>
+    <t>34670-43-4</t>
+  </si>
+  <si>
+    <t>1241681-80-0</t>
+  </si>
+  <si>
+    <t>1016163-79-3</t>
+  </si>
+  <si>
+    <t>1176270-25-9</t>
+  </si>
+  <si>
+    <t>Nα-Fmoc-Nδ-Azido-D-ornithine</t>
+  </si>
+  <si>
+    <t>50913-12-7</t>
+  </si>
+  <si>
+    <t>13594-51-9</t>
+  </si>
+  <si>
+    <t>156-86-5</t>
+  </si>
+  <si>
+    <t>1313054-60-2</t>
+  </si>
+  <si>
+    <t>2978-24-7</t>
+  </si>
+  <si>
+    <t>1360651-24-6</t>
+  </si>
+  <si>
+    <t>851960-68-4</t>
+  </si>
+  <si>
+    <t>L-Photo-Met</t>
+  </si>
+  <si>
+    <t>23235-01-0</t>
+  </si>
+  <si>
+    <t>220497-98-3</t>
+  </si>
+  <si>
+    <t>3326-32-7</t>
+  </si>
+  <si>
+    <t>4-Carboxy-L-phenylalanine</t>
+  </si>
+  <si>
+    <t>126109-42-0</t>
+  </si>
+  <si>
+    <t>4-Carboxy-D-phenylalanine</t>
+  </si>
+  <si>
+    <t>1991-87-3</t>
+  </si>
+  <si>
+    <t>49759-61-7</t>
+  </si>
+  <si>
+    <t>54594-06-8</t>
+  </si>
+  <si>
+    <t>149597-91-1</t>
+  </si>
+  <si>
+    <t>114926-39-5</t>
+  </si>
+  <si>
+    <t>170080-13-4</t>
+  </si>
+  <si>
+    <t>252049-14-2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@H](C)(CC))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[C:2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
-    </r>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <t>D-Ile-PEG4(CH2)</t>
   </si>
   <si>
     <r>
@@ -2018,22 +5058,67 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H]([C@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCOCCOCCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
       <t>[NH2:1]</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCCC(=O)O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@@H]([C@@H](C)(CC))C(=O)O(CCOCCOCC[N]=[N+]=[N-])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CC=1NC=NC1)</t>
+      <t>(C)[C@@H]([C@H](O)C)</t>
     </r>
     <r>
       <rPr>
@@ -2061,6 +5146,36 @@
         <color theme="4"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
+      <t>[NH1:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(C)[C@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
       <t>[NH2:1]</t>
     </r>
     <r>
@@ -2071,7 +5186,32 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CC=1NC=NC1)</t>
+      <t>[C@@H]([C@@H](O)C)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[NH2:1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C@H]([C@H](O)C)</t>
     </r>
     <r>
       <rPr>
@@ -2109,25 +5249,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
+      <t>[C@H](CCCN(=[N+]=[N-]))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[C:2](=O)O</t>
     </r>
   </si>
   <si>
@@ -2147,1717 +5279,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCCN)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCN)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@@H](C)(CC))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@H](C)(CC))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccccc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccccc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC(C)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC(C)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1c[nH]c2ccccc12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1c[nH]c2ccccc12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCSC)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCSC)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CS)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CS)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C(=O)C[C@H](N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C(=O)C[C@@H](N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(C)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C(C)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CO)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CO)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCC(=O)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCC(=O)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccc(O)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccc(O)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC(=O)O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC(=O)O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCC(=O)O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCC(=O)O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C(CO))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(CO))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@H](C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CS(CNC(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CS(CNC(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccc(OC)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccc(OC)cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1c(C)cc(O)cc(C)1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1c(C)cc(O)cc(C)1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CCC</t>
+      <t>[C@H](CCCNC(N)=O)</t>
     </r>
     <r>
       <rPr>
@@ -3869,1680 +5291,13 @@
       </rPr>
       <t>[C:2](=O)O</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](C(C1=CC2=CC=CC=C2C=C1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(C1=CC2=CC=CC=C2C=C1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=O)CCCC[C@@H]1[C@@H]2NC(=O)N[C@@H]2CS1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CCCCCNC(=O)CCCC[C@H]1[C@H]2NC(=O)N[C@H]2CS1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=O)C1=CC=C(C(=O)C2=CC=CC=C2)C=C1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C1C=CC(C(=O)C2=CC=CC=C2)=CC=1)[C@H](CCCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](Cc1ccc([N]=[N+]=[N-])cc1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C([N]=[N+]=[N-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCN(=[N+]=[N-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCNC(=N)N([N+](=O)[O-]))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCN(C(=O)C))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCNC(N)=O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@@H]1C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCCCNC(=N)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCCCNC(=N)N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CCNC(N)=N)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CCC(C)1N=N1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=S)N(C1=CC=C(C2=C1C(=O)OC23C4=C(C=C(C=C4)O)OC5=C3C=CC(=C5)O)))CCCCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC1C=CC(C(=O)O)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C(=O)O)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC1C=CC(C)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC=C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](C(C1C=CC=CC=1)(C1C=CC=CC=1))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC=C(C)C=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C2C=CC=CC=2)=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC1C=CC(C(C)(C)(C))=CC=1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C)[C@@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>Exception</t>
-  </si>
-  <si>
-    <t>Just for the last position</t>
-  </si>
-  <si>
-    <t>D-Propargylglycine</t>
-  </si>
-  <si>
-    <t>{pra}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H](CC#C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H](CC#C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>[NH2]</t>
-  </si>
-  <si>
-    <t>71-00-1</t>
-  </si>
-  <si>
-    <t>351-50-8</t>
-  </si>
-  <si>
-    <t>74-79-3</t>
-  </si>
-  <si>
-    <t>157-06-2</t>
-  </si>
-  <si>
-    <t>56-87-1</t>
-  </si>
-  <si>
-    <t>923-27-3</t>
-  </si>
-  <si>
-    <t>73-32-5</t>
-  </si>
-  <si>
-    <t>319-78-8</t>
-  </si>
-  <si>
-    <t>63-91-2</t>
-  </si>
-  <si>
-    <t>673-06-3</t>
-  </si>
-  <si>
-    <t>61-90-5</t>
-  </si>
-  <si>
-    <t>328-38-1</t>
-  </si>
-  <si>
-    <t>54-12-6</t>
-  </si>
-  <si>
-    <t>153-94-6</t>
-  </si>
-  <si>
-    <t>56-41-7</t>
-  </si>
-  <si>
-    <t>338-69-2</t>
-  </si>
-  <si>
-    <t>63-68-3</t>
-  </si>
-  <si>
-    <t>348-67-4</t>
-  </si>
-  <si>
-    <t>147-85-3</t>
-  </si>
-  <si>
-    <t>344-25-2</t>
-  </si>
-  <si>
-    <t>52-90-4</t>
-  </si>
-  <si>
-    <t>921-01-7</t>
-  </si>
-  <si>
-    <t>70-47-3</t>
-  </si>
-  <si>
-    <t>2058-58-4</t>
-  </si>
-  <si>
-    <t>72-18-4</t>
-  </si>
-  <si>
-    <t>640-68-6</t>
-  </si>
-  <si>
-    <t>56-40-6</t>
-  </si>
-  <si>
-    <t>56-45-1</t>
-  </si>
-  <si>
-    <t>312-84-5</t>
-  </si>
-  <si>
-    <t>26700-71-0</t>
-  </si>
-  <si>
-    <t>5959-95-5</t>
-  </si>
-  <si>
-    <t>60-18-4</t>
-  </si>
-  <si>
-    <t>556-02-5</t>
-  </si>
-  <si>
-    <t>56-84-8</t>
-  </si>
-  <si>
-    <t>1783-96-6</t>
-  </si>
-  <si>
-    <t>56-86-0</t>
-  </si>
-  <si>
-    <t>6893-26-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@@H]([C@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>80-68-2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH2:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[C@H]([C@@H](O)C)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>672-15-1</t>
-  </si>
-  <si>
-    <t>6027-21-0</t>
-  </si>
-  <si>
-    <t>3913-67-5</t>
-  </si>
-  <si>
-    <t>600-21-5</t>
-  </si>
-  <si>
-    <t>19647-70-2</t>
-  </si>
-  <si>
-    <t>168300-88-7</t>
-  </si>
-  <si>
-    <t>6230-11-1</t>
-  </si>
-  <si>
-    <t>201335-88-8</t>
-  </si>
-  <si>
-    <t>206060-54-0</t>
-  </si>
-  <si>
-    <t>136771-16-9</t>
-  </si>
-  <si>
-    <t>2812-28-4</t>
-  </si>
-  <si>
-    <t>2812-27-3</t>
-  </si>
-  <si>
-    <t>56-12-2</t>
-  </si>
-  <si>
-    <t>144-98-9</t>
-  </si>
-  <si>
-    <t>24830-94-2</t>
-  </si>
-  <si>
-    <t>76985-09-6</t>
-  </si>
-  <si>
-    <t>58438-03-2</t>
-  </si>
-  <si>
-    <t>741281-41-4</t>
-  </si>
-  <si>
-    <t>34670-43-4</t>
-  </si>
-  <si>
-    <t>1241681-80-0</t>
-  </si>
-  <si>
-    <t>1016163-79-3</t>
-  </si>
-  <si>
-    <t>1176270-25-9</t>
-  </si>
-  <si>
-    <t>Nα-Fmoc-Nδ-Azido-D-ornithine</t>
-  </si>
-  <si>
-    <t>50913-12-7</t>
-  </si>
-  <si>
-    <t>13594-51-9</t>
-  </si>
-  <si>
-    <t>156-86-5</t>
-  </si>
-  <si>
-    <t>1313054-60-2</t>
-  </si>
-  <si>
-    <t>2978-24-7</t>
-  </si>
-  <si>
-    <t>1360651-24-6</t>
-  </si>
-  <si>
-    <t>851960-68-4</t>
-  </si>
-  <si>
-    <t>L-Photo-Met</t>
-  </si>
-  <si>
-    <t>23235-01-0</t>
-  </si>
-  <si>
-    <t>220497-98-3</t>
-  </si>
-  <si>
-    <t>3326-32-7</t>
-  </si>
-  <si>
-    <t>4-Carboxy-L-phenylalanine</t>
-  </si>
-  <si>
-    <t>126109-42-0</t>
-  </si>
-  <si>
-    <t>4-Carboxy-D-phenylalanine</t>
-  </si>
-  <si>
-    <t>1991-87-3</t>
-  </si>
-  <si>
-    <t>49759-61-7</t>
-  </si>
-  <si>
-    <t>54594-06-8</t>
-  </si>
-  <si>
-    <t>149597-91-1</t>
-  </si>
-  <si>
-    <t>114926-39-5</t>
-  </si>
-  <si>
-    <t>170080-13-4</t>
-  </si>
-  <si>
-    <t>252049-14-2</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>{ac-P}</t>
-  </si>
-  <si>
-    <t>68-95-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>{gly-P}</t>
-  </si>
-  <si>
-    <t>N-Acetyl-L-Proline</t>
-  </si>
-  <si>
-    <t>Glycyl-L-Proline</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)CN)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>704-15-4</t>
-  </si>
-  <si>
-    <t>N-PEG4-L-Proline</t>
-  </si>
-  <si>
-    <t>{PEG4-P}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[N:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CCOCCOCCOCCOC(=O)O)1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1CCC[C@H]1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-  </si>
-  <si>
-    <t>{P-am}</t>
-  </si>
-  <si>
-    <t>L-Prolinamide</t>
-  </si>
-  <si>
-    <t>7531-52-4</t>
-  </si>
-  <si>
-    <t>N-Acetyl-L-tryptophan</t>
-  </si>
-  <si>
-    <t>{ac-W}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="4"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[NH1:1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(C(=O)C)[C@@H](Cc1c[nH]c2ccccc12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>[C:2](=O)O</t>
-    </r>
-  </si>
-  <si>
-    <t>1218-34-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5623,6 +5378,12 @@
       <color theme="4"/>
       <name val="Calibri (Body)"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -5650,7 +5411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5692,14 +5453,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5731,11 +5486,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5795,7 +5547,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="110">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="105">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6214,26 +5966,6 @@
   </rv>
   <rv s="0">
     <v>104</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>105</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>106</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>107</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>108</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>109</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -6355,11 +6087,6 @@
   <rel r:id="rId103"/>
   <rel r:id="rId104"/>
   <rel r:id="rId105"/>
-  <rel r:id="rId106"/>
-  <rel r:id="rId107"/>
-  <rel r:id="rId108"/>
-  <rel r:id="rId109"/>
-  <rel r:id="rId110"/>
 </richValueRels>
 </file>
 
@@ -6660,7 +6387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="6" customWidth="1"/>
@@ -6670,7 +6397,7 @@
     <col min="5" max="5" width="35" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="103.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" style="24" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" style="22" customWidth="1"/>
     <col min="9" max="9" width="24.33203125" style="2" customWidth="1"/>
     <col min="10" max="10" width="35.33203125" style="10" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="2" customWidth="1"/>
@@ -6699,7 +6426,7 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
@@ -6708,8 +6435,8 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="18" t="s">
-        <v>319</v>
+      <c r="K1" s="16" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6720,7 +6447,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -6732,10 +6459,10 @@
         <v>13</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>326</v>
+        <v>231</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>312</v>
       </c>
       <c r="I2" s="2" t="e" vm="1">
         <v>#VALUE!</v>
@@ -6749,7 +6476,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -6761,10 +6488,10 @@
         <v>16</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>327</v>
+        <v>232</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>313</v>
       </c>
       <c r="I3" s="2" t="e" vm="2">
         <v>#VALUE!</v>
@@ -6778,7 +6505,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
@@ -6790,10 +6517,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>328</v>
+        <v>233</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>314</v>
       </c>
       <c r="I4" s="2" t="e" vm="3">
         <v>#VALUE!</v>
@@ -6807,7 +6534,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -6819,10 +6546,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>329</v>
+        <v>234</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>315</v>
       </c>
       <c r="I5" s="2" t="e" vm="4">
         <v>#VALUE!</v>
@@ -6836,7 +6563,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>21</v>
@@ -6848,10 +6575,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>330</v>
+        <v>235</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>316</v>
       </c>
       <c r="I6" s="2" t="e" vm="5">
         <v>#VALUE!</v>
@@ -6865,7 +6592,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>23</v>
@@ -6877,10 +6604,10 @@
         <v>16</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>331</v>
+        <v>236</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="I7" s="2" t="e" vm="6">
         <v>#VALUE!</v>
@@ -6894,7 +6621,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>25</v>
@@ -6906,10 +6633,10 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>332</v>
+        <v>397</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>318</v>
       </c>
       <c r="I8" s="2" t="e" vm="7">
         <v>#VALUE!</v>
@@ -6923,7 +6650,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>27</v>
@@ -6935,10 +6662,10 @@
         <v>16</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>333</v>
+        <v>398</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>319</v>
       </c>
       <c r="I9" s="2" t="e" vm="8">
         <v>#VALUE!</v>
@@ -6952,7 +6679,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -6964,10 +6691,10 @@
         <v>13</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>334</v>
+        <v>237</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>320</v>
       </c>
       <c r="I10" s="2" t="e" vm="9">
         <v>#VALUE!</v>
@@ -6981,7 +6708,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>31</v>
@@ -6993,10 +6720,10 @@
         <v>16</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>335</v>
+        <v>238</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>321</v>
       </c>
       <c r="I11" s="2" t="e" vm="10">
         <v>#VALUE!</v>
@@ -7010,7 +6737,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -7022,10 +6749,10 @@
         <v>13</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>336</v>
+        <v>239</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>322</v>
       </c>
       <c r="I12" s="2" t="e" vm="11">
         <v>#VALUE!</v>
@@ -7039,7 +6766,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>34</v>
@@ -7051,10 +6778,10 @@
         <v>16</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>337</v>
+        <v>240</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>323</v>
       </c>
       <c r="I13" s="2" t="e" vm="12">
         <v>#VALUE!</v>
@@ -7068,7 +6795,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
@@ -7080,10 +6807,10 @@
         <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>338</v>
+        <v>242</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>324</v>
       </c>
       <c r="I14" s="2" t="e" vm="13">
         <v>#VALUE!</v>
@@ -7097,7 +6824,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>38</v>
@@ -7109,10 +6836,10 @@
         <v>16</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>339</v>
+        <v>241</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>325</v>
       </c>
       <c r="I15" s="2" t="e" vm="14">
         <v>#VALUE!</v>
@@ -7126,7 +6853,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>40</v>
@@ -7138,10 +6865,10 @@
         <v>13</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>340</v>
+        <v>243</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>326</v>
       </c>
       <c r="I16" s="2" t="e" vm="15">
         <v>#VALUE!</v>
@@ -7155,7 +6882,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>42</v>
@@ -7167,10 +6894,10 @@
         <v>16</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>341</v>
+        <v>244</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>327</v>
       </c>
       <c r="I17" s="2" t="e" vm="16">
         <v>#VALUE!</v>
@@ -7184,7 +6911,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>44</v>
@@ -7196,10 +6923,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>342</v>
+        <v>245</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>328</v>
       </c>
       <c r="I18" s="2" t="e" vm="17">
         <v>#VALUE!</v>
@@ -7213,7 +6940,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>46</v>
@@ -7225,10 +6952,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>343</v>
+        <v>246</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>329</v>
       </c>
       <c r="I19" s="2" t="e" vm="18">
         <v>#VALUE!</v>
@@ -7242,7 +6969,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
@@ -7254,10 +6981,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>344</v>
+        <v>247</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>330</v>
       </c>
       <c r="I20" s="2" t="e" vm="19">
         <v>#VALUE!</v>
@@ -7271,7 +6998,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>50</v>
@@ -7283,10 +7010,10 @@
         <v>16</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>345</v>
+        <v>248</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>331</v>
       </c>
       <c r="I21" s="2" t="e" vm="20">
         <v>#VALUE!</v>
@@ -7300,7 +7027,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>52</v>
@@ -7312,10 +7039,10 @@
         <v>13</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>346</v>
+        <v>249</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>332</v>
       </c>
       <c r="I22" s="2" t="e" vm="21">
         <v>#VALUE!</v>
@@ -7329,7 +7056,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>54</v>
@@ -7341,10 +7068,10 @@
         <v>16</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>347</v>
+        <v>250</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>333</v>
       </c>
       <c r="I23" s="2" t="e" vm="22">
         <v>#VALUE!</v>
@@ -7358,7 +7085,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>56</v>
@@ -7370,10 +7097,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>348</v>
+        <v>251</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>334</v>
       </c>
       <c r="I24" s="2" t="e" vm="23">
         <v>#VALUE!</v>
@@ -7387,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>58</v>
@@ -7399,10 +7126,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>349</v>
+        <v>252</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>335</v>
       </c>
       <c r="I25" s="2" t="e" vm="24">
         <v>#VALUE!</v>
@@ -7416,7 +7143,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>60</v>
@@ -7428,10 +7155,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>350</v>
+        <v>254</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>336</v>
       </c>
       <c r="I26" s="2" t="e" vm="25">
         <v>#VALUE!</v>
@@ -7445,7 +7172,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>62</v>
@@ -7457,10 +7184,10 @@
         <v>16</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>351</v>
+        <v>253</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>337</v>
       </c>
       <c r="I27" s="2" t="e" vm="26">
         <v>#VALUE!</v>
@@ -7474,7 +7201,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>64</v>
@@ -7486,10 +7213,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>352</v>
+        <v>255</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>338</v>
       </c>
       <c r="I28" s="2" t="e" vm="27">
         <v>#VALUE!</v>
@@ -7503,7 +7230,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>66</v>
@@ -7515,10 +7242,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="H29" s="24" t="s">
-        <v>353</v>
+        <v>257</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>339</v>
       </c>
       <c r="I29" s="2" t="e" vm="28">
         <v>#VALUE!</v>
@@ -7532,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>68</v>
@@ -7544,10 +7271,10 @@
         <v>16</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>354</v>
+        <v>256</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>340</v>
       </c>
       <c r="I30" s="2" t="e" vm="29">
         <v>#VALUE!</v>
@@ -7561,7 +7288,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>70</v>
@@ -7573,10 +7300,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="H31" s="24" t="s">
-        <v>355</v>
+        <v>258</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>341</v>
       </c>
       <c r="I31" s="2" t="e" vm="30">
         <v>#VALUE!</v>
@@ -7590,7 +7317,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>72</v>
@@ -7602,10 +7329,10 @@
         <v>16</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H32" s="24" t="s">
-        <v>356</v>
+        <v>259</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>342</v>
       </c>
       <c r="I32" s="2" t="e" vm="31">
         <v>#VALUE!</v>
@@ -7619,7 +7346,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>74</v>
@@ -7631,10 +7358,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="H33" s="24" t="s">
-        <v>357</v>
+        <v>260</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>343</v>
       </c>
       <c r="I33" s="2" t="e" vm="32">
         <v>#VALUE!</v>
@@ -7648,7 +7375,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>76</v>
@@ -7660,10 +7387,10 @@
         <v>16</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H34" s="24" t="s">
-        <v>358</v>
+        <v>261</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>344</v>
       </c>
       <c r="I34" s="2" t="e" vm="33">
         <v>#VALUE!</v>
@@ -7677,7 +7404,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>16</v>
@@ -7689,10 +7416,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="H35" s="24" t="s">
-        <v>359</v>
+        <v>262</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>345</v>
       </c>
       <c r="I35" s="2" t="e" vm="34">
         <v>#VALUE!</v>
@@ -7706,7 +7433,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>79</v>
@@ -7718,10 +7445,10 @@
         <v>16</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>360</v>
+        <v>263</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>346</v>
       </c>
       <c r="I36" s="2" t="e" vm="35">
         <v>#VALUE!</v>
@@ -7735,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>81</v>
@@ -7747,10 +7474,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="H37" s="24" t="s">
-        <v>361</v>
+        <v>264</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>347</v>
       </c>
       <c r="I37" s="2" t="e" vm="36">
         <v>#VALUE!</v>
@@ -7764,7 +7491,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>83</v>
@@ -7776,10 +7503,10 @@
         <v>16</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="H38" s="24" t="s">
-        <v>362</v>
+        <v>265</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>348</v>
       </c>
       <c r="I38" s="2" t="e" vm="37">
         <v>#VALUE!</v>
@@ -7793,7 +7520,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>85</v>
@@ -7805,10 +7532,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>364</v>
+        <v>349</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>350</v>
       </c>
       <c r="I39" s="2" t="e" vm="38">
         <v>#VALUE!</v>
@@ -7822,7 +7549,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>87</v>
@@ -7834,10 +7561,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="H40" s="24" t="s">
-        <v>364</v>
+        <v>351</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>350</v>
       </c>
       <c r="I40" s="2" t="e" vm="39">
         <v>#VALUE!</v>
@@ -7851,7 +7578,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>89</v>
@@ -7863,10 +7590,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>366</v>
+        <v>266</v>
+      </c>
+      <c r="H41" s="22" t="s">
+        <v>352</v>
       </c>
       <c r="I41" s="2" t="e" vm="40">
         <v>#VALUE!</v>
@@ -7880,7 +7607,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>91</v>
@@ -7892,10 +7619,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>367</v>
+        <v>267</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>353</v>
       </c>
       <c r="I42" s="2" t="e" vm="41">
         <v>#VALUE!</v>
@@ -7909,7 +7636,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>93</v>
@@ -7921,10 +7648,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>368</v>
+        <v>268</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>354</v>
       </c>
       <c r="I43" s="2" t="e" vm="42">
         <v>#VALUE!</v>
@@ -7938,7 +7665,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>95</v>
@@ -7950,10 +7677,10 @@
         <v>16</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>369</v>
+        <v>269</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>355</v>
       </c>
       <c r="I44" s="2" t="e" vm="43">
         <v>#VALUE!</v>
@@ -7967,7 +7694,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>97</v>
@@ -7978,11 +7705,11 @@
       <c r="F45" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>370</v>
+      <c r="G45" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>356</v>
       </c>
       <c r="I45" s="2" t="e" vm="44">
         <v>#VALUE!</v>
@@ -7996,7 +7723,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>99</v>
@@ -8007,11 +7734,11 @@
       <c r="F46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>371</v>
+      <c r="G46" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="H46" s="22" t="s">
+        <v>357</v>
       </c>
       <c r="I46" s="2" t="e" vm="45">
         <v>#VALUE!</v>
@@ -8025,7 +7752,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>101</v>
@@ -8036,11 +7763,11 @@
       <c r="F47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>372</v>
+      <c r="G47" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>358</v>
       </c>
       <c r="I47" s="2" t="e" vm="46">
         <v>#VALUE!</v>
@@ -8054,7 +7781,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>103</v>
@@ -8065,11 +7792,11 @@
       <c r="F48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>373</v>
+      <c r="G48" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="H48" s="22" t="s">
+        <v>359</v>
       </c>
       <c r="I48" s="2" t="e" vm="47">
         <v>#VALUE!</v>
@@ -8083,7 +7810,7 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>105</v>
@@ -8095,10 +7822,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>374</v>
+        <v>274</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>360</v>
       </c>
       <c r="I49" s="2" t="e" vm="48">
         <v>#VALUE!</v>
@@ -8112,7 +7839,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>107</v>
@@ -8124,10 +7851,10 @@
         <v>16</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="H50" s="24" t="s">
-        <v>375</v>
+        <v>275</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>361</v>
       </c>
       <c r="I50" s="2" t="e" vm="49">
         <v>#VALUE!</v>
@@ -8150,8 +7877,8 @@
       <c r="G51" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H51" s="24" t="s">
-        <v>410</v>
+      <c r="H51" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I51" s="2" t="e" vm="50">
         <v>#VALUE!</v>
@@ -8177,8 +7904,8 @@
       <c r="G52" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H52" s="24" t="s">
-        <v>410</v>
+      <c r="H52" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I52" s="2" t="e" vm="51">
         <v>#VALUE!</v>
@@ -8204,8 +7931,8 @@
       <c r="G53" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H53" s="24" t="s">
-        <v>410</v>
+      <c r="H53" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I53" s="2" t="e" vm="52">
         <v>#VALUE!</v>
@@ -8231,8 +7958,8 @@
       <c r="G54" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H54" s="24" t="s">
-        <v>410</v>
+      <c r="H54" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I54" s="2" t="e" vm="53">
         <v>#VALUE!</v>
@@ -8258,8 +7985,8 @@
       <c r="G55" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="H55" s="24" t="s">
-        <v>410</v>
+      <c r="H55" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I55" s="2" t="e" vm="54">
         <v>#VALUE!</v>
@@ -8285,8 +8012,8 @@
       <c r="G56" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>410</v>
+      <c r="H56" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I56" s="2" t="e" vm="55">
         <v>#VALUE!</v>
@@ -8312,8 +8039,8 @@
       <c r="G57" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>410</v>
+      <c r="H57" s="23" t="s">
+        <v>396</v>
       </c>
       <c r="I57" s="2" t="e" vm="56">
         <v>#VALUE!</v>
@@ -8330,7 +8057,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>130</v>
@@ -8341,10 +8068,10 @@
       <c r="F58" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="H58" s="25" t="s">
+      <c r="G58" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="H58" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I58" s="2" t="e" vm="57">
@@ -8365,21 +8092,21 @@
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>134</v>
+      <c r="E59" s="24" t="s">
+        <v>400</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="H59" s="25" t="s">
+      <c r="G59" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="H59" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I59" s="2" t="e" vm="58">
@@ -8400,7 +8127,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>135</v>
@@ -8411,10 +8138,10 @@
       <c r="F60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="H60" s="25" t="s">
+      <c r="G60" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="H60" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I60" s="2" t="e" vm="59">
@@ -8435,7 +8162,7 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>136</v>
@@ -8446,10 +8173,10 @@
       <c r="F61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G61" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="H61" s="25" t="s">
+      <c r="G61" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="H61" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I61" s="2" t="e" vm="60">
@@ -8470,7 +8197,7 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>138</v>
@@ -8481,10 +8208,10 @@
       <c r="F62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G62" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="H62" s="25" t="s">
+      <c r="G62" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="H62" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I62" s="2" t="e" vm="61">
@@ -8505,7 +8232,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>140</v>
@@ -8516,10 +8243,10 @@
       <c r="F63" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="H63" s="25" t="s">
+      <c r="G63" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="H63" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I63" s="2" t="e" vm="62">
@@ -8540,7 +8267,7 @@
         <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>141</v>
@@ -8551,10 +8278,10 @@
       <c r="F64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="H64" s="25" t="s">
+      <c r="G64" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="H64" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I64" s="2" t="e" vm="63">
@@ -8575,7 +8302,7 @@
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>143</v>
@@ -8586,10 +8313,10 @@
       <c r="F65" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="H65" s="25" t="s">
+      <c r="G65" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="H65" s="23" t="s">
         <v>222</v>
       </c>
       <c r="I65" s="2" t="e" vm="64">
@@ -8610,7 +8337,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>145</v>
@@ -8622,10 +8349,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="H66" s="24" t="s">
-        <v>376</v>
+        <v>404</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>362</v>
       </c>
       <c r="I66" s="2" t="e" vm="65">
         <v>#VALUE!</v>
@@ -8639,7 +8366,7 @@
         <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>147</v>
@@ -8651,10 +8378,10 @@
         <v>16</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>377</v>
+        <v>405</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>363</v>
       </c>
       <c r="I67" s="2" t="e" vm="66">
         <v>#VALUE!</v>
@@ -8668,7 +8395,7 @@
         <v>10</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>149</v>
@@ -8679,11 +8406,11 @@
       <c r="F68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="H68" s="24" t="s">
-        <v>378</v>
+      <c r="G68" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>364</v>
       </c>
       <c r="I68" s="2" t="e" vm="67">
         <v>#VALUE!</v>
@@ -8697,7 +8424,7 @@
         <v>10</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>151</v>
@@ -8709,10 +8436,10 @@
         <v>13</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>379</v>
+        <v>406</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>365</v>
       </c>
       <c r="I69" s="2" t="e" vm="68">
         <v>#VALUE!</v>
@@ -8726,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>153</v>
@@ -8738,10 +8465,10 @@
         <v>16</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="H70" s="24" t="s">
-        <v>380</v>
+        <v>407</v>
+      </c>
+      <c r="H70" s="22" t="s">
+        <v>366</v>
       </c>
       <c r="I70" s="2" t="e" vm="69">
         <v>#VALUE!</v>
@@ -8755,7 +8482,7 @@
         <v>10</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>155</v>
@@ -8767,10 +8494,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="H71" s="24" t="s">
-        <v>382</v>
+        <v>277</v>
+      </c>
+      <c r="H71" s="22" t="s">
+        <v>368</v>
       </c>
       <c r="I71" s="2" t="e" vm="70">
         <v>#VALUE!</v>
@@ -8784,7 +8511,7 @@
         <v>10</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>157</v>
@@ -8796,10 +8523,10 @@
         <v>16</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>381</v>
+        <v>278</v>
+      </c>
+      <c r="H72" s="22" t="s">
+        <v>367</v>
       </c>
       <c r="I72" s="2" t="e" vm="71">
         <v>#VALUE!</v>
@@ -8813,7 +8540,7 @@
         <v>10</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>159</v>
@@ -8824,10 +8551,10 @@
       <c r="F73" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G73" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="H73" s="24" t="s">
+      <c r="G73" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="H73" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I73" s="11" t="e" vm="72">
@@ -8842,7 +8569,7 @@
         <v>10</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>161</v>
@@ -8853,10 +8580,10 @@
       <c r="F74" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G74" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="H74" s="24" t="s">
+      <c r="G74" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="H74" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I74" s="2" t="e" vm="73">
@@ -8871,7 +8598,7 @@
         <v>10</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>163</v>
@@ -8882,11 +8609,11 @@
       <c r="F75" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G75" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="H75" s="24" t="s">
-        <v>383</v>
+      <c r="G75" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="H75" s="22" t="s">
+        <v>369</v>
       </c>
       <c r="I75" s="2" t="e" vm="74">
         <v>#VALUE!</v>
@@ -8900,7 +8627,7 @@
         <v>10</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>165</v>
@@ -8911,10 +8638,10 @@
       <c r="F76" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G76" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="H76" s="24" t="s">
+      <c r="G76" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="H76" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I76" s="2" t="e" vm="75">
@@ -8929,7 +8656,7 @@
         <v>10</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>167</v>
@@ -8940,10 +8667,10 @@
       <c r="F77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G77" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="H77" s="24" t="s">
+      <c r="G77" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="H77" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I77" s="2" t="e" vm="76">
@@ -8958,7 +8685,7 @@
         <v>10</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>169</v>
@@ -8969,11 +8696,11 @@
       <c r="F78" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G78" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>384</v>
+      <c r="G78" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H78" s="22" t="s">
+        <v>370</v>
       </c>
       <c r="I78" s="2" t="e" vm="77">
         <v>#VALUE!</v>
@@ -8987,7 +8714,7 @@
         <v>10</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>171</v>
@@ -8998,11 +8725,11 @@
       <c r="F79" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G79" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="H79" s="24" t="s">
-        <v>385</v>
+      <c r="G79" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="H79" s="22" t="s">
+        <v>371</v>
       </c>
       <c r="I79" s="2" t="e" vm="78">
         <v>#VALUE!</v>
@@ -9016,7 +8743,7 @@
         <v>10</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>173</v>
@@ -9027,11 +8754,11 @@
       <c r="F80" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="H80" s="24" t="s">
-        <v>386</v>
+      <c r="G80" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H80" s="22" t="s">
+        <v>372</v>
       </c>
       <c r="I80" s="2" t="e" vm="79">
         <v>#VALUE!</v>
@@ -9045,22 +8772,22 @@
         <v>10</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>388</v>
+      <c r="E81" s="20" t="s">
+        <v>374</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G81" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="H81" s="24" t="s">
-        <v>387</v>
+      <c r="G81" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="H81" s="22" t="s">
+        <v>373</v>
       </c>
       <c r="I81" s="2" t="e" vm="80">
         <v>#VALUE!</v>
@@ -9074,7 +8801,7 @@
         <v>10</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>176</v>
@@ -9085,11 +8812,11 @@
       <c r="F82" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G82" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="H82" s="24" t="s">
-        <v>389</v>
+      <c r="G82" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>375</v>
       </c>
       <c r="I82" s="2" t="e" vm="81">
         <v>#VALUE!</v>
@@ -9112,8 +8839,8 @@
       <c r="G83" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H83" s="24" t="s">
-        <v>410</v>
+      <c r="H83" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I83" s="2" t="e" vm="82">
         <v>#VALUE!</v>
@@ -9130,7 +8857,7 @@
         <v>10</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>181</v>
@@ -9141,10 +8868,10 @@
       <c r="F84" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G84" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="H84" s="24" t="s">
+      <c r="G84" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="H84" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I84" s="2" t="e" vm="83">
@@ -9159,7 +8886,7 @@
         <v>10</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>183</v>
@@ -9171,10 +8898,10 @@
         <v>16</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="H85" s="24" t="s">
-        <v>390</v>
+        <v>409</v>
+      </c>
+      <c r="H85" s="22" t="s">
+        <v>376</v>
       </c>
       <c r="I85" s="2" t="e" vm="84">
         <v>#VALUE!</v>
@@ -9188,7 +8915,7 @@
         <v>10</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>185</v>
@@ -9200,10 +8927,10 @@
         <v>16</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="H86" s="24" t="s">
-        <v>345</v>
+        <v>289</v>
+      </c>
+      <c r="H86" s="22" t="s">
+        <v>331</v>
       </c>
       <c r="I86" s="2" t="e" vm="85">
         <v>#VALUE!</v>
@@ -9217,7 +8944,7 @@
         <v>10</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>187</v>
@@ -9228,11 +8955,11 @@
       <c r="F87" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="H87" s="24" t="s">
-        <v>391</v>
+      <c r="G87" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="H87" s="22" t="s">
+        <v>377</v>
       </c>
       <c r="I87" s="2" t="e" vm="86">
         <v>#VALUE!</v>
@@ -9246,7 +8973,7 @@
         <v>10</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>189</v>
@@ -9257,11 +8984,11 @@
       <c r="F88" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G88" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="H88" s="24" t="s">
-        <v>392</v>
+      <c r="G88" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="H88" s="22" t="s">
+        <v>378</v>
       </c>
       <c r="I88" s="2" t="e" vm="87">
         <v>#VALUE!</v>
@@ -9275,7 +9002,7 @@
         <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>191</v>
@@ -9287,10 +9014,10 @@
         <v>16</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="H89" s="24" t="s">
-        <v>393</v>
+        <v>292</v>
+      </c>
+      <c r="H89" s="22" t="s">
+        <v>379</v>
       </c>
       <c r="I89" s="2" t="e" vm="88">
         <v>#VALUE!</v>
@@ -9304,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>193</v>
@@ -9315,11 +9042,11 @@
       <c r="F90" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G90" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="H90" s="24" t="s">
-        <v>394</v>
+      <c r="G90" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="H90" s="22" t="s">
+        <v>380</v>
       </c>
       <c r="I90" s="2" t="e" vm="89">
         <v>#VALUE!</v>
@@ -9333,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>195</v>
@@ -9344,10 +9071,10 @@
       <c r="F91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G91" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="H91" s="24" t="s">
+      <c r="G91" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="H91" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I91" s="2" t="e" vm="90">
@@ -9362,22 +9089,22 @@
         <v>10</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E92" s="22" t="s">
-        <v>396</v>
+      <c r="E92" s="20" t="s">
+        <v>382</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G92" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="H92" s="24" t="s">
-        <v>395</v>
+      <c r="G92" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="H92" s="22" t="s">
+        <v>381</v>
       </c>
       <c r="I92" s="2" t="e" vm="91">
         <v>#VALUE!</v>
@@ -9391,9 +9118,9 @@
         <v>10</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D93" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="D93" s="17" t="s">
         <v>198</v>
       </c>
       <c r="E93" s="2" t="s">
@@ -9402,11 +9129,11 @@
       <c r="F93" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G93" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>397</v>
+      <c r="G93" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="H93" s="22" t="s">
+        <v>383</v>
       </c>
       <c r="I93" s="2" t="e" vm="92">
         <v>#VALUE!</v>
@@ -9420,22 +9147,22 @@
         <v>10</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="F94" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E94" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="F94" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G94" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>398</v>
+      <c r="G94" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="H94" s="22" t="s">
+        <v>384</v>
       </c>
       <c r="I94" s="2" t="e" vm="93">
         <v>#VALUE!</v>
@@ -9449,7 +9176,7 @@
         <v>10</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>200</v>
@@ -9460,11 +9187,11 @@
       <c r="F95" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="H95" s="24" t="s">
-        <v>399</v>
+      <c r="G95" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="H95" s="22" t="s">
+        <v>385</v>
       </c>
       <c r="I95" s="2" t="e" vm="94">
         <v>#VALUE!</v>
@@ -9487,11 +9214,11 @@
       <c r="E96" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G96" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="H96" s="24" t="s">
-        <v>410</v>
+      <c r="G96" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H96" s="22" t="s">
+        <v>396</v>
       </c>
       <c r="I96" s="2" t="e" vm="95">
         <v>#VALUE!</v>
@@ -9500,7 +9227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -9508,28 +9235,28 @@
         <v>10</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E97" s="22" t="s">
-        <v>400</v>
+      <c r="E97" s="20" t="s">
+        <v>386</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G97" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="H97" s="24" t="s">
-        <v>401</v>
+      <c r="G97" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="H97" s="22" t="s">
+        <v>387</v>
       </c>
       <c r="I97" s="2" t="e" vm="96">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -9537,28 +9264,28 @@
         <v>10</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>402</v>
-      </c>
-      <c r="F98" s="22" t="s">
+      <c r="E98" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="F98" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G98" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="H98" s="24" t="s">
+      <c r="G98" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="H98" s="22" t="s">
         <v>222</v>
       </c>
       <c r="I98" s="2" t="e" vm="97">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -9566,28 +9293,28 @@
         <v>10</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E99" s="22" t="s">
+      <c r="E99" s="20" t="s">
         <v>208</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="H99" s="24" t="s">
-        <v>403</v>
+      <c r="G99" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H99" s="22" t="s">
+        <v>389</v>
       </c>
       <c r="I99" s="2" t="e" vm="98">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -9595,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>209</v>
@@ -9606,17 +9333,17 @@
       <c r="F100" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G100" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="H100" s="24" t="s">
-        <v>404</v>
+      <c r="G100" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="H100" s="22" t="s">
+        <v>390</v>
       </c>
       <c r="I100" s="2" t="e" vm="99">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -9624,28 +9351,28 @@
         <v>10</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>211</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="H101" s="24" t="s">
-        <v>405</v>
+      <c r="G101" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="I101" s="2" t="e" vm="100">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -9653,7 +9380,7 @@
         <v>10</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>212</v>
@@ -9664,17 +9391,17 @@
       <c r="F102" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G102" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="H102" s="24" t="s">
-        <v>406</v>
+      <c r="G102" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="H102" s="22" t="s">
+        <v>392</v>
       </c>
       <c r="I102" s="2" t="e" vm="101">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -9682,7 +9409,7 @@
         <v>10</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>214</v>
@@ -9693,17 +9420,17 @@
       <c r="F103" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G103" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="H103" s="24" t="s">
-        <v>407</v>
+      <c r="G103" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="H103" s="22" t="s">
+        <v>393</v>
       </c>
       <c r="I103" s="2" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -9711,7 +9438,7 @@
         <v>10</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>212</v>
@@ -9722,17 +9449,17 @@
       <c r="F104" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G104" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="H104" s="24" t="s">
-        <v>408</v>
+      <c r="G104" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="H104" s="22" t="s">
+        <v>394</v>
       </c>
       <c r="I104" s="2" t="e" vm="103">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -9740,7 +9467,7 @@
         <v>10</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>217</v>
@@ -9751,17 +9478,17 @@
       <c r="F105" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G105" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="H105" s="24" t="s">
-        <v>409</v>
+      <c r="G105" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="H105" s="22" t="s">
+        <v>395</v>
       </c>
       <c r="I105" s="2" t="e" vm="104">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -9769,7 +9496,7 @@
         <v>10</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>219</v>
@@ -9781,185 +9508,41 @@
         <v>16</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H106" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="H106" s="22" t="s">
         <v>221</v>
       </c>
       <c r="I106" s="2" t="e" vm="105">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2">
-        <v>130</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D107" s="26" t="s">
-        <v>411</v>
-      </c>
-      <c r="E107" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="27" t="s">
-        <v>413</v>
-      </c>
-      <c r="H107" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="I107" s="2" t="e" vm="106">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J107" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="K107" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="2">
-        <v>131</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D108" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E108" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="27" t="s">
-        <v>417</v>
-      </c>
-      <c r="H108" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="I108" s="2" t="e" vm="107">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J108" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="K108" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2">
-        <v>132</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D109" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="E109" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="H109" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="I109" s="2" t="e" vm="108">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J109" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="K109" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="2">
-        <v>133</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D110" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="E110" s="26" t="s">
-        <v>424</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="H110" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="I110" s="2" t="e" vm="109">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J110" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="K110" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="2">
-        <v>134</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="D111" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="E111" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="27" t="s">
-        <v>428</v>
-      </c>
-      <c r="H111" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="I111" s="2" t="e" vm="110">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="2"/>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="2"/>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="2"/>
+    </row>
+    <row r="110" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="2"/>
+    </row>
+    <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="2"/>
+    </row>
+    <row r="112" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="2"/>
@@ -9994,48 +9577,9 @@
       <c r="B118" s="3"/>
       <c r="C118" s="2"/>
     </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="2"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="2"/>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="2"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="2"/>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="2"/>
-      <c r="B121" s="3"/>
-      <c r="C121" s="2"/>
-    </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="2"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="2"/>
-    </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="2"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="2"/>
-    </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="2"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="2"/>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="2"/>
-      <c r="B125" s="3"/>
-      <c r="C125" s="2"/>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="2"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="2"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{1AD03261-8AC5-410F-A743-A6D54D43FB41}"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
